--- a/output/CS_SFIAFormat/sfiaformat_mapping_cosine_SkillNER RAKE_KeyBERT_CS.xlsx
+++ b/output/CS_SFIAFormat/sfiaformat_mapping_cosine_SkillNER RAKE_KeyBERT_CS.xlsx
@@ -518,7 +518,7 @@
       </c>
       <c r="F4" t="inlineStr"/>
       <c r="G4" t="n">
-        <v>0.2064</v>
+        <v>0.3641</v>
       </c>
       <c r="H4" t="n">
         <v>0.2493</v>
@@ -535,10 +535,10 @@
       <c r="D5" t="inlineStr"/>
       <c r="E5" t="inlineStr"/>
       <c r="F5" t="n">
-        <v>0.2178</v>
+        <v>0.2296</v>
       </c>
       <c r="G5" t="n">
-        <v>0.2014</v>
+        <v>0.2119</v>
       </c>
       <c r="H5" t="inlineStr"/>
     </row>
@@ -555,10 +555,10 @@
         <v>0.2466</v>
       </c>
       <c r="F6" t="n">
-        <v>0.2247</v>
+        <v>0.2256</v>
       </c>
       <c r="G6" t="n">
-        <v>0.201</v>
+        <v>0.2109</v>
       </c>
       <c r="H6" t="inlineStr"/>
     </row>
@@ -590,7 +590,7 @@
       <c r="C8" t="inlineStr"/>
       <c r="D8" t="inlineStr"/>
       <c r="E8" t="n">
-        <v>0.215</v>
+        <v>0.221</v>
       </c>
       <c r="F8" t="inlineStr"/>
       <c r="G8" t="n">
@@ -640,7 +640,7 @@
       <c r="C11" t="inlineStr"/>
       <c r="D11" t="inlineStr"/>
       <c r="E11" t="n">
-        <v>0.2149</v>
+        <v>0.2359</v>
       </c>
       <c r="F11" t="n">
         <v>0.2648</v>
@@ -767,7 +767,7 @@
       <c r="D19" t="inlineStr"/>
       <c r="E19" t="inlineStr"/>
       <c r="F19" t="n">
-        <v>0.2024</v>
+        <v>0.2484</v>
       </c>
       <c r="G19" t="n">
         <v>0.2258</v>
@@ -784,7 +784,7 @@
       </c>
       <c r="B20" t="inlineStr"/>
       <c r="C20" t="n">
-        <v>0.2068</v>
+        <v>0.2155</v>
       </c>
       <c r="D20" t="n">
         <v>0.2041</v>
@@ -870,13 +870,13 @@
         <v>0.3042</v>
       </c>
       <c r="E25" t="n">
-        <v>0.2956</v>
+        <v>0.3045</v>
       </c>
       <c r="F25" t="n">
-        <v>0.2187</v>
+        <v>0.2225</v>
       </c>
       <c r="G25" t="n">
-        <v>0.2311</v>
+        <v>0.2351</v>
       </c>
       <c r="H25" t="n">
         <v>0.3586</v>
@@ -908,7 +908,7 @@
       <c r="E27" t="inlineStr"/>
       <c r="F27" t="inlineStr"/>
       <c r="G27" t="n">
-        <v>0.247</v>
+        <v>0.2968</v>
       </c>
       <c r="H27" t="inlineStr"/>
     </row>
@@ -1039,13 +1039,13 @@
         <v>0.2192</v>
       </c>
       <c r="F35" t="n">
-        <v>0.2132</v>
+        <v>0.2239</v>
       </c>
       <c r="G35" t="n">
-        <v>0.2472</v>
+        <v>0.3408</v>
       </c>
       <c r="H35" t="n">
-        <v>0.2353</v>
+        <v>0.3644</v>
       </c>
     </row>
     <row r="36">
@@ -1090,7 +1090,7 @@
       <c r="C38" t="inlineStr"/>
       <c r="D38" t="inlineStr"/>
       <c r="E38" t="n">
-        <v>0.2035</v>
+        <v>0.2156</v>
       </c>
       <c r="F38" t="n">
         <v>0.2349</v>
@@ -1177,19 +1177,19 @@
         <v>0.2376</v>
       </c>
       <c r="D43" t="n">
-        <v>0.2148</v>
+        <v>0.3352</v>
       </c>
       <c r="E43" t="n">
-        <v>0.2151</v>
+        <v>0.299</v>
       </c>
       <c r="F43" t="n">
-        <v>0.2312</v>
+        <v>0.2327</v>
       </c>
       <c r="G43" t="n">
         <v>0.2341</v>
       </c>
       <c r="H43" t="n">
-        <v>0.2294</v>
+        <v>0.2594</v>
       </c>
     </row>
     <row r="44">
@@ -1270,7 +1270,7 @@
       </c>
       <c r="B49" t="inlineStr"/>
       <c r="C49" t="n">
-        <v>0.2001</v>
+        <v>0.3305</v>
       </c>
       <c r="D49" t="inlineStr"/>
       <c r="E49" t="n">
@@ -1311,7 +1311,7 @@
       </c>
       <c r="E51" t="inlineStr"/>
       <c r="F51" t="n">
-        <v>0.2277</v>
+        <v>0.2413</v>
       </c>
       <c r="G51" t="n">
         <v>0.2134</v>
@@ -1326,7 +1326,7 @@
       </c>
       <c r="B52" t="inlineStr"/>
       <c r="C52" t="n">
-        <v>0.2141</v>
+        <v>0.2451</v>
       </c>
       <c r="D52" t="n">
         <v>0.216</v>
@@ -1371,13 +1371,13 @@
         <v>0.2849</v>
       </c>
       <c r="D54" t="n">
-        <v>0.2317</v>
+        <v>0.2377</v>
       </c>
       <c r="E54" t="n">
         <v>0.2572</v>
       </c>
       <c r="F54" t="n">
-        <v>0.2174</v>
+        <v>0.3422</v>
       </c>
       <c r="G54" t="n">
         <v>0.2796</v>
@@ -1392,7 +1392,7 @@
       </c>
       <c r="B55" t="inlineStr"/>
       <c r="C55" t="n">
-        <v>0.2064</v>
+        <v>0.2338</v>
       </c>
       <c r="D55" t="inlineStr"/>
       <c r="E55" t="inlineStr"/>
@@ -1433,14 +1433,14 @@
       <c r="B57" t="inlineStr"/>
       <c r="C57" t="inlineStr"/>
       <c r="D57" t="n">
-        <v>0.2016</v>
+        <v>0.2655</v>
       </c>
       <c r="E57" t="n">
         <v>0.2297</v>
       </c>
       <c r="F57" t="inlineStr"/>
       <c r="G57" t="n">
-        <v>0.2418</v>
+        <v>0.2507</v>
       </c>
       <c r="H57" t="inlineStr"/>
     </row>
@@ -1467,10 +1467,10 @@
         </is>
       </c>
       <c r="B59" t="n">
-        <v>0.2184</v>
+        <v>0.2641</v>
       </c>
       <c r="C59" t="n">
-        <v>0.2157</v>
+        <v>0.3282</v>
       </c>
       <c r="D59" t="n">
         <v>0.2726</v>
@@ -1479,7 +1479,7 @@
         <v>0.2611</v>
       </c>
       <c r="F59" t="n">
-        <v>0.2133</v>
+        <v>0.2308</v>
       </c>
       <c r="G59" t="n">
         <v>0.2254</v>
@@ -1609,7 +1609,7 @@
         <v>0.2079</v>
       </c>
       <c r="F67" t="n">
-        <v>0.2802</v>
+        <v>0.3157</v>
       </c>
       <c r="G67" t="inlineStr"/>
       <c r="H67" t="inlineStr"/>
@@ -1656,16 +1656,16 @@
       </c>
       <c r="B70" t="inlineStr"/>
       <c r="C70" t="n">
-        <v>0.2377</v>
+        <v>0.2553</v>
       </c>
       <c r="D70" t="n">
-        <v>0.2006</v>
+        <v>0.2023</v>
       </c>
       <c r="E70" t="n">
         <v>0.2009</v>
       </c>
       <c r="F70" t="n">
-        <v>0.2189</v>
+        <v>0.2554</v>
       </c>
       <c r="G70" t="inlineStr"/>
       <c r="H70" t="inlineStr"/>
@@ -1682,13 +1682,13 @@
         <v>0.2517</v>
       </c>
       <c r="E71" t="n">
-        <v>0.2535</v>
+        <v>0.2856</v>
       </c>
       <c r="F71" t="n">
         <v>0.2327</v>
       </c>
       <c r="G71" t="n">
-        <v>0.2215</v>
+        <v>0.3004</v>
       </c>
       <c r="H71" t="n">
         <v>0.2278</v>
@@ -1706,10 +1706,10 @@
       </c>
       <c r="D72" t="inlineStr"/>
       <c r="E72" t="n">
-        <v>0.2146</v>
+        <v>0.244</v>
       </c>
       <c r="F72" t="n">
-        <v>0.2204</v>
+        <v>0.2347</v>
       </c>
       <c r="G72" t="inlineStr"/>
       <c r="H72" t="inlineStr"/>
@@ -1765,10 +1765,10 @@
       <c r="B75" t="inlineStr"/>
       <c r="C75" t="inlineStr"/>
       <c r="D75" t="n">
-        <v>0.2183</v>
+        <v>0.2371</v>
       </c>
       <c r="E75" t="n">
-        <v>0.2033</v>
+        <v>0.2754</v>
       </c>
       <c r="F75" t="n">
         <v>0.2147</v>
@@ -1800,7 +1800,7 @@
       </c>
       <c r="B77" t="inlineStr"/>
       <c r="C77" t="n">
-        <v>0.2258</v>
+        <v>0.2719</v>
       </c>
       <c r="D77" t="n">
         <v>0.2221</v>
@@ -1868,7 +1868,7 @@
       </c>
       <c r="B81" t="inlineStr"/>
       <c r="C81" t="n">
-        <v>0.2161</v>
+        <v>0.2382</v>
       </c>
       <c r="D81" t="inlineStr"/>
       <c r="E81" t="n">
@@ -1878,7 +1878,7 @@
         <v>0.2267</v>
       </c>
       <c r="G81" t="n">
-        <v>0.208</v>
+        <v>0.2116</v>
       </c>
       <c r="H81" t="inlineStr"/>
     </row>
@@ -1893,7 +1893,7 @@
       <c r="D82" t="inlineStr"/>
       <c r="E82" t="inlineStr"/>
       <c r="F82" t="n">
-        <v>0.2134</v>
+        <v>0.2136</v>
       </c>
       <c r="G82" t="inlineStr"/>
       <c r="H82" t="inlineStr"/>
@@ -1955,7 +1955,7 @@
       </c>
       <c r="E86" t="inlineStr"/>
       <c r="F86" t="n">
-        <v>0.2225</v>
+        <v>0.2643</v>
       </c>
       <c r="G86" t="inlineStr"/>
       <c r="H86" t="inlineStr"/>
@@ -2039,7 +2039,7 @@
       <c r="D91" t="inlineStr"/>
       <c r="E91" t="inlineStr"/>
       <c r="F91" t="n">
-        <v>0.2115</v>
+        <v>0.2729</v>
       </c>
       <c r="G91" t="inlineStr"/>
       <c r="H91" t="inlineStr"/>
@@ -2051,16 +2051,16 @@
         </is>
       </c>
       <c r="B92" t="n">
-        <v>0.2121</v>
+        <v>0.2402</v>
       </c>
       <c r="C92" t="n">
-        <v>0.2039</v>
+        <v>0.247</v>
       </c>
       <c r="D92" t="n">
         <v>0.204</v>
       </c>
       <c r="E92" t="n">
-        <v>0.2065</v>
+        <v>0.2294</v>
       </c>
       <c r="F92" t="inlineStr"/>
       <c r="G92" t="inlineStr"/>
@@ -2103,7 +2103,7 @@
         <v>0.3134</v>
       </c>
       <c r="F94" t="n">
-        <v>0.2085</v>
+        <v>0.3022</v>
       </c>
       <c r="G94" t="inlineStr"/>
       <c r="H94" t="inlineStr"/>
@@ -2348,7 +2348,7 @@
       <c r="E108" t="inlineStr"/>
       <c r="F108" t="inlineStr"/>
       <c r="G108" t="n">
-        <v>0.2089</v>
+        <v>0.2498</v>
       </c>
       <c r="H108" t="inlineStr"/>
     </row>
@@ -2436,7 +2436,7 @@
         <v>0.2326</v>
       </c>
       <c r="E113" t="n">
-        <v>0.2124</v>
+        <v>0.2229</v>
       </c>
       <c r="F113" t="n">
         <v>0.2433</v>
@@ -2502,13 +2502,13 @@
         <v>0.2956</v>
       </c>
       <c r="E117" t="n">
-        <v>0.2173</v>
+        <v>0.352</v>
       </c>
       <c r="F117" t="n">
-        <v>0.2161</v>
+        <v>0.2841</v>
       </c>
       <c r="G117" t="n">
-        <v>0.2092</v>
+        <v>0.2302</v>
       </c>
       <c r="H117" t="inlineStr"/>
     </row>
@@ -2550,7 +2550,7 @@
       <c r="C120" t="inlineStr"/>
       <c r="D120" t="inlineStr"/>
       <c r="E120" t="n">
-        <v>0.2429</v>
+        <v>0.261</v>
       </c>
       <c r="F120" t="inlineStr"/>
       <c r="G120" t="inlineStr"/>
@@ -2816,7 +2816,7 @@
         <v>0.2169</v>
       </c>
       <c r="C138" t="n">
-        <v>0.2023</v>
+        <v>0.345</v>
       </c>
       <c r="D138" t="inlineStr"/>
       <c r="E138" t="inlineStr"/>
@@ -2890,7 +2890,7 @@
         <v>0.2839</v>
       </c>
       <c r="G142" t="n">
-        <v>0.2076</v>
+        <v>0.3581</v>
       </c>
       <c r="H142" t="inlineStr"/>
     </row>
@@ -2911,7 +2911,7 @@
       </c>
       <c r="G143" t="inlineStr"/>
       <c r="H143" t="n">
-        <v>0.232</v>
+        <v>0.2432</v>
       </c>
     </row>
     <row r="144">
@@ -2944,7 +2944,7 @@
         <v>0.3523</v>
       </c>
       <c r="G145" t="n">
-        <v>0.2072</v>
+        <v>0.235</v>
       </c>
       <c r="H145" t="inlineStr"/>
     </row>
